--- a/lorenzo-playwright-kdf/excelFramework/testcases/User Creation/LSTP_User_Creation_WF001.xlsx
+++ b/lorenzo-playwright-kdf/excelFramework/testcases/User Creation/LSTP_User_Creation_WF001.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bkrishnan6\ORBIS PAS UKI-LZO\lorenzo-playwright-kdf\excelFramework\testcases\User Creation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB3AF5A1-0819-43BA-91A0-EC1EA77E85D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{437D4D77-EA6C-4DE5-8C10-F3DD1712545E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-1335" yWindow="-16320" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{385191F1-EE6F-4B29-BAB0-0783BFEA82AF}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="3" xr2:uid="{385191F1-EE6F-4B29-BAB0-0783BFEA82AF}"/>
   </bookViews>
   <sheets>
     <sheet name="TestExecution" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="390" uniqueCount="209">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="389" uniqueCount="208">
   <si>
     <t>StepNo</t>
   </si>
@@ -78,9 +78,6 @@
   </si>
   <si>
     <t>launchUrl</t>
-  </si>
-  <si>
-    <t>http://dxcappchne8097a.cscidp.net/webclient_sso/extlogon.aspx?idp=oidnatlogon&amp;IsClientInfoNotRequired=true</t>
   </si>
   <si>
     <t>Login with valid credentials</t>
@@ -1122,25 +1119,22 @@
       <c r="F2" t="s">
         <v>12</v>
       </c>
-      <c r="J2" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" t="s">
         <v>14</v>
       </c>
-      <c r="C3" t="s">
+      <c r="F3" t="s">
         <v>15</v>
       </c>
-      <c r="F3" t="s">
+      <c r="J3" t="s">
         <v>16</v>
-      </c>
-      <c r="J3" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
@@ -1148,13 +1142,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" t="s">
         <v>18</v>
       </c>
-      <c r="C4" t="s">
+      <c r="F4" t="s">
         <v>19</v>
-      </c>
-      <c r="F4" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
@@ -1162,16 +1156,16 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" t="s">
         <v>21</v>
       </c>
-      <c r="C5" t="s">
-        <v>19</v>
-      </c>
-      <c r="D5" t="s">
+      <c r="F5" t="s">
         <v>22</v>
-      </c>
-      <c r="F5" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
@@ -1179,13 +1173,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F6" t="s">
         <v>19</v>
-      </c>
-      <c r="F6" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
@@ -1193,16 +1187,16 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" t="s">
+        <v>18</v>
+      </c>
+      <c r="D7" t="s">
         <v>25</v>
       </c>
-      <c r="C7" t="s">
-        <v>19</v>
-      </c>
-      <c r="D7" t="s">
-        <v>26</v>
-      </c>
       <c r="F7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
@@ -1210,13 +1204,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
@@ -1224,13 +1218,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
+        <v>28</v>
+      </c>
+      <c r="F9" t="s">
         <v>29</v>
       </c>
-      <c r="F9" t="s">
+      <c r="J9" t="s">
         <v>30</v>
-      </c>
-      <c r="J9" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
@@ -1238,19 +1232,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
+        <v>31</v>
+      </c>
+      <c r="C10" t="s">
+        <v>27</v>
+      </c>
+      <c r="D10" t="s">
         <v>32</v>
       </c>
-      <c r="C10" t="s">
-        <v>28</v>
-      </c>
-      <c r="D10" t="s">
+      <c r="F10" t="s">
         <v>33</v>
       </c>
-      <c r="F10" t="s">
+      <c r="J10" t="s">
         <v>34</v>
-      </c>
-      <c r="J10" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
@@ -1258,19 +1252,19 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
+        <v>35</v>
+      </c>
+      <c r="C11" t="s">
+        <v>27</v>
+      </c>
+      <c r="D11" t="s">
         <v>36</v>
       </c>
-      <c r="C11" t="s">
-        <v>28</v>
-      </c>
-      <c r="D11" t="s">
+      <c r="F11" t="s">
+        <v>33</v>
+      </c>
+      <c r="K11" t="s">
         <v>37</v>
-      </c>
-      <c r="F11" t="s">
-        <v>34</v>
-      </c>
-      <c r="K11" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
@@ -1278,19 +1272,19 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
+        <v>38</v>
+      </c>
+      <c r="C12" t="s">
+        <v>27</v>
+      </c>
+      <c r="D12" t="s">
         <v>39</v>
       </c>
-      <c r="C12" t="s">
-        <v>28</v>
-      </c>
-      <c r="D12" t="s">
+      <c r="F12" t="s">
         <v>40</v>
       </c>
-      <c r="F12" t="s">
+      <c r="K12" t="s">
         <v>41</v>
-      </c>
-      <c r="K12" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
@@ -1298,19 +1292,19 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
+        <v>42</v>
+      </c>
+      <c r="C13" t="s">
+        <v>27</v>
+      </c>
+      <c r="D13" t="s">
         <v>43</v>
       </c>
-      <c r="C13" t="s">
-        <v>28</v>
-      </c>
-      <c r="D13" t="s">
+      <c r="F13" t="s">
+        <v>40</v>
+      </c>
+      <c r="K13" t="s">
         <v>44</v>
-      </c>
-      <c r="F13" t="s">
-        <v>41</v>
-      </c>
-      <c r="K13" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
@@ -1318,19 +1312,19 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
+        <v>45</v>
+      </c>
+      <c r="C14" t="s">
+        <v>27</v>
+      </c>
+      <c r="D14" t="s">
         <v>46</v>
       </c>
-      <c r="C14" t="s">
-        <v>28</v>
-      </c>
-      <c r="D14" t="s">
+      <c r="F14" t="s">
+        <v>33</v>
+      </c>
+      <c r="K14" t="s">
         <v>47</v>
-      </c>
-      <c r="F14" t="s">
-        <v>34</v>
-      </c>
-      <c r="K14" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
@@ -1338,16 +1332,16 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
+        <v>48</v>
+      </c>
+      <c r="C15" t="s">
+        <v>27</v>
+      </c>
+      <c r="D15" t="s">
         <v>49</v>
       </c>
-      <c r="C15" t="s">
-        <v>28</v>
-      </c>
-      <c r="D15" t="s">
-        <v>50</v>
-      </c>
       <c r="F15" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
@@ -1355,16 +1349,16 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
+        <v>50</v>
+      </c>
+      <c r="C16" t="s">
+        <v>27</v>
+      </c>
+      <c r="D16" t="s">
         <v>51</v>
       </c>
-      <c r="C16" t="s">
-        <v>28</v>
-      </c>
-      <c r="D16" t="s">
-        <v>52</v>
-      </c>
       <c r="F16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
@@ -1372,19 +1366,19 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
+        <v>52</v>
+      </c>
+      <c r="C17" t="s">
+        <v>27</v>
+      </c>
+      <c r="D17" t="s">
         <v>53</v>
       </c>
-      <c r="C17" t="s">
-        <v>28</v>
-      </c>
-      <c r="D17" t="s">
+      <c r="F17" t="s">
+        <v>33</v>
+      </c>
+      <c r="K17" t="s">
         <v>54</v>
-      </c>
-      <c r="F17" t="s">
-        <v>34</v>
-      </c>
-      <c r="K17" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.25">
@@ -1392,16 +1386,16 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
+        <v>55</v>
+      </c>
+      <c r="C18" t="s">
+        <v>27</v>
+      </c>
+      <c r="D18" t="s">
         <v>56</v>
       </c>
-      <c r="C18" t="s">
-        <v>28</v>
-      </c>
-      <c r="D18" t="s">
-        <v>57</v>
-      </c>
       <c r="F18" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
@@ -1409,13 +1403,13 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C19" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F19" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
@@ -1423,16 +1417,16 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
+        <v>58</v>
+      </c>
+      <c r="C20" t="s">
+        <v>27</v>
+      </c>
+      <c r="D20" t="s">
         <v>59</v>
       </c>
-      <c r="C20" t="s">
-        <v>28</v>
-      </c>
-      <c r="D20" t="s">
-        <v>60</v>
-      </c>
       <c r="F20" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
@@ -1440,13 +1434,13 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C21" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F21" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
@@ -1454,19 +1448,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
+        <v>61</v>
+      </c>
+      <c r="C22" t="s">
+        <v>27</v>
+      </c>
+      <c r="D22" t="s">
         <v>62</v>
       </c>
-      <c r="C22" t="s">
-        <v>28</v>
-      </c>
-      <c r="D22" t="s">
+      <c r="F22" t="s">
+        <v>33</v>
+      </c>
+      <c r="K22" t="s">
         <v>63</v>
-      </c>
-      <c r="F22" t="s">
-        <v>34</v>
-      </c>
-      <c r="K22" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
@@ -1474,16 +1468,16 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
+        <v>64</v>
+      </c>
+      <c r="C23" t="s">
+        <v>27</v>
+      </c>
+      <c r="D23" t="s">
         <v>65</v>
       </c>
-      <c r="C23" t="s">
-        <v>28</v>
-      </c>
-      <c r="D23" t="s">
-        <v>66</v>
-      </c>
       <c r="F23" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
@@ -1491,13 +1485,13 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C24" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F24" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
@@ -1505,19 +1499,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
+        <v>67</v>
+      </c>
+      <c r="C25" t="s">
+        <v>27</v>
+      </c>
+      <c r="D25" t="s">
         <v>68</v>
       </c>
-      <c r="C25" t="s">
-        <v>28</v>
-      </c>
-      <c r="D25" t="s">
+      <c r="F25" t="s">
+        <v>40</v>
+      </c>
+      <c r="K25" t="s">
         <v>69</v>
-      </c>
-      <c r="F25" t="s">
-        <v>41</v>
-      </c>
-      <c r="K25" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
@@ -1525,16 +1519,16 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
+        <v>70</v>
+      </c>
+      <c r="C26" t="s">
+        <v>27</v>
+      </c>
+      <c r="D26" t="s">
         <v>71</v>
       </c>
-      <c r="C26" t="s">
-        <v>28</v>
-      </c>
-      <c r="D26" t="s">
-        <v>72</v>
-      </c>
       <c r="F26" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.25">
@@ -1542,13 +1536,13 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C27" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F27" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
@@ -1556,19 +1550,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
+        <v>73</v>
+      </c>
+      <c r="C28" t="s">
+        <v>27</v>
+      </c>
+      <c r="D28" t="s">
         <v>74</v>
       </c>
-      <c r="C28" t="s">
-        <v>28</v>
-      </c>
-      <c r="D28" t="s">
+      <c r="F28" t="s">
+        <v>33</v>
+      </c>
+      <c r="K28" t="s">
         <v>75</v>
-      </c>
-      <c r="F28" t="s">
-        <v>34</v>
-      </c>
-      <c r="K28" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
@@ -1576,16 +1570,16 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
+        <v>76</v>
+      </c>
+      <c r="C29" t="s">
+        <v>27</v>
+      </c>
+      <c r="D29" t="s">
         <v>77</v>
       </c>
-      <c r="C29" t="s">
-        <v>28</v>
-      </c>
-      <c r="D29" t="s">
-        <v>78</v>
-      </c>
       <c r="F29" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
@@ -1593,13 +1587,13 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C30" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F30" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
@@ -1607,16 +1601,16 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
+        <v>79</v>
+      </c>
+      <c r="C31" t="s">
+        <v>27</v>
+      </c>
+      <c r="D31" t="s">
         <v>80</v>
       </c>
-      <c r="C31" t="s">
-        <v>28</v>
-      </c>
-      <c r="D31" t="s">
-        <v>81</v>
-      </c>
       <c r="F31" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.25">
@@ -1624,16 +1618,16 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
+        <v>81</v>
+      </c>
+      <c r="C32" t="s">
+        <v>27</v>
+      </c>
+      <c r="D32" t="s">
         <v>82</v>
       </c>
-      <c r="C32" t="s">
-        <v>28</v>
-      </c>
-      <c r="D32" t="s">
-        <v>83</v>
-      </c>
       <c r="F32" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.25">
@@ -1641,16 +1635,16 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C33" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D33" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F33" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.25">
@@ -1658,13 +1652,13 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C34" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F34" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.25">
@@ -1672,19 +1666,19 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
+        <v>85</v>
+      </c>
+      <c r="C35" t="s">
+        <v>27</v>
+      </c>
+      <c r="D35" t="s">
         <v>86</v>
       </c>
-      <c r="C35" t="s">
-        <v>28</v>
-      </c>
-      <c r="D35" t="s">
+      <c r="F35" t="s">
+        <v>40</v>
+      </c>
+      <c r="K35" t="s">
         <v>87</v>
-      </c>
-      <c r="F35" t="s">
-        <v>41</v>
-      </c>
-      <c r="K35" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.25">
@@ -1692,19 +1686,19 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
+        <v>88</v>
+      </c>
+      <c r="C36" t="s">
+        <v>27</v>
+      </c>
+      <c r="D36" t="s">
         <v>89</v>
       </c>
-      <c r="C36" t="s">
-        <v>28</v>
-      </c>
-      <c r="D36" t="s">
+      <c r="F36" t="s">
+        <v>33</v>
+      </c>
+      <c r="K36" t="s">
         <v>90</v>
-      </c>
-      <c r="F36" t="s">
-        <v>34</v>
-      </c>
-      <c r="K36" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.25">
@@ -1712,16 +1706,16 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
+        <v>91</v>
+      </c>
+      <c r="C37" t="s">
+        <v>27</v>
+      </c>
+      <c r="D37" t="s">
         <v>92</v>
       </c>
-      <c r="C37" t="s">
-        <v>28</v>
-      </c>
-      <c r="D37" t="s">
-        <v>93</v>
-      </c>
       <c r="F37" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.25">
@@ -1729,13 +1723,13 @@
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C38" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F38" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.25">
@@ -1743,16 +1737,16 @@
         <v>38</v>
       </c>
       <c r="B39" t="s">
+        <v>94</v>
+      </c>
+      <c r="C39" t="s">
+        <v>27</v>
+      </c>
+      <c r="D39" t="s">
         <v>95</v>
       </c>
-      <c r="C39" t="s">
-        <v>28</v>
-      </c>
-      <c r="D39" t="s">
-        <v>96</v>
-      </c>
       <c r="F39" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.25">
@@ -1760,13 +1754,13 @@
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C40" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F40" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.25">
@@ -1774,19 +1768,19 @@
         <v>40</v>
       </c>
       <c r="B41" t="s">
+        <v>97</v>
+      </c>
+      <c r="C41" t="s">
+        <v>27</v>
+      </c>
+      <c r="D41" t="s">
         <v>98</v>
       </c>
-      <c r="C41" t="s">
-        <v>28</v>
-      </c>
-      <c r="D41" t="s">
+      <c r="F41" t="s">
         <v>99</v>
       </c>
-      <c r="F41" t="s">
+      <c r="J41" t="s">
         <v>100</v>
-      </c>
-      <c r="J41" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.25">
@@ -1794,16 +1788,16 @@
         <v>41</v>
       </c>
       <c r="B42" t="s">
+        <v>101</v>
+      </c>
+      <c r="C42" t="s">
+        <v>27</v>
+      </c>
+      <c r="D42" t="s">
         <v>102</v>
       </c>
-      <c r="C42" t="s">
-        <v>28</v>
-      </c>
-      <c r="D42" t="s">
-        <v>103</v>
-      </c>
       <c r="F42" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.25">
@@ -1811,13 +1805,13 @@
         <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C43" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F43" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.25">
@@ -1825,19 +1819,19 @@
         <v>43</v>
       </c>
       <c r="B44" t="s">
+        <v>104</v>
+      </c>
+      <c r="C44" t="s">
         <v>105</v>
       </c>
-      <c r="C44" t="s">
-        <v>106</v>
-      </c>
       <c r="D44" t="s">
+        <v>32</v>
+      </c>
+      <c r="F44" t="s">
         <v>33</v>
       </c>
-      <c r="F44" t="s">
+      <c r="J44" t="s">
         <v>34</v>
-      </c>
-      <c r="J44" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.25">
@@ -1845,16 +1839,16 @@
         <v>44</v>
       </c>
       <c r="B45" t="s">
+        <v>106</v>
+      </c>
+      <c r="C45" t="s">
+        <v>105</v>
+      </c>
+      <c r="D45" t="s">
         <v>107</v>
       </c>
-      <c r="C45" t="s">
-        <v>106</v>
-      </c>
-      <c r="D45" t="s">
-        <v>108</v>
-      </c>
       <c r="F45" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.25">
@@ -1862,13 +1856,13 @@
         <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C46" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F46" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.25">
@@ -1876,22 +1870,22 @@
         <v>46</v>
       </c>
       <c r="B47" t="s">
+        <v>109</v>
+      </c>
+      <c r="C47" t="s">
+        <v>105</v>
+      </c>
+      <c r="D47" t="s">
+        <v>32</v>
+      </c>
+      <c r="F47" t="s">
         <v>110</v>
       </c>
-      <c r="C47" t="s">
-        <v>106</v>
-      </c>
-      <c r="D47" t="s">
-        <v>33</v>
-      </c>
-      <c r="F47" t="s">
+      <c r="G47" t="s">
         <v>111</v>
       </c>
-      <c r="G47" t="s">
+      <c r="H47" t="s">
         <v>112</v>
-      </c>
-      <c r="H47" t="s">
-        <v>113</v>
       </c>
       <c r="J47" t="b">
         <v>1</v>
@@ -1902,16 +1896,16 @@
         <v>47</v>
       </c>
       <c r="B48" t="s">
+        <v>113</v>
+      </c>
+      <c r="C48" t="s">
+        <v>105</v>
+      </c>
+      <c r="D48" t="s">
         <v>114</v>
       </c>
-      <c r="C48" t="s">
-        <v>106</v>
-      </c>
-      <c r="D48" t="s">
-        <v>115</v>
-      </c>
       <c r="F48" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.25">
@@ -1919,13 +1913,13 @@
         <v>48</v>
       </c>
       <c r="B49" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C49" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F49" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.25">
@@ -1933,16 +1927,16 @@
         <v>49</v>
       </c>
       <c r="B50" t="s">
+        <v>116</v>
+      </c>
+      <c r="C50" t="s">
+        <v>105</v>
+      </c>
+      <c r="D50" t="s">
         <v>117</v>
       </c>
-      <c r="C50" t="s">
-        <v>106</v>
-      </c>
-      <c r="D50" t="s">
-        <v>118</v>
-      </c>
       <c r="F50" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.25">
@@ -1950,19 +1944,19 @@
         <v>50</v>
       </c>
       <c r="B51" t="s">
+        <v>118</v>
+      </c>
+      <c r="C51" t="s">
+        <v>105</v>
+      </c>
+      <c r="D51" t="s">
+        <v>43</v>
+      </c>
+      <c r="F51" t="s">
+        <v>40</v>
+      </c>
+      <c r="K51" t="s">
         <v>119</v>
-      </c>
-      <c r="C51" t="s">
-        <v>106</v>
-      </c>
-      <c r="D51" t="s">
-        <v>44</v>
-      </c>
-      <c r="F51" t="s">
-        <v>41</v>
-      </c>
-      <c r="K51" t="s">
-        <v>120</v>
       </c>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.25">
@@ -1970,19 +1964,19 @@
         <v>51</v>
       </c>
       <c r="B52" t="s">
+        <v>120</v>
+      </c>
+      <c r="C52" t="s">
+        <v>105</v>
+      </c>
+      <c r="D52" t="s">
+        <v>46</v>
+      </c>
+      <c r="F52" t="s">
+        <v>33</v>
+      </c>
+      <c r="K52" t="s">
         <v>121</v>
-      </c>
-      <c r="C52" t="s">
-        <v>106</v>
-      </c>
-      <c r="D52" t="s">
-        <v>47</v>
-      </c>
-      <c r="F52" t="s">
-        <v>34</v>
-      </c>
-      <c r="K52" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.25">
@@ -1990,16 +1984,16 @@
         <v>52</v>
       </c>
       <c r="B53" t="s">
+        <v>122</v>
+      </c>
+      <c r="C53" t="s">
+        <v>105</v>
+      </c>
+      <c r="D53" t="s">
         <v>123</v>
       </c>
-      <c r="C53" t="s">
-        <v>106</v>
-      </c>
-      <c r="D53" t="s">
-        <v>124</v>
-      </c>
       <c r="F53" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.25">
@@ -2007,13 +2001,13 @@
         <v>53</v>
       </c>
       <c r="B54" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C54" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F54" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.25">
@@ -2021,16 +2015,16 @@
         <v>54</v>
       </c>
       <c r="B55" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C55" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D55" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F55" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.25">
@@ -2038,13 +2032,13 @@
         <v>55</v>
       </c>
       <c r="B56" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C56" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F56" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.25">
@@ -2052,16 +2046,16 @@
         <v>56</v>
       </c>
       <c r="B57" t="s">
+        <v>127</v>
+      </c>
+      <c r="C57" t="s">
+        <v>105</v>
+      </c>
+      <c r="D57" t="s">
         <v>128</v>
       </c>
-      <c r="C57" t="s">
-        <v>106</v>
-      </c>
-      <c r="D57" t="s">
-        <v>129</v>
-      </c>
       <c r="F57" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.25">
@@ -2069,13 +2063,13 @@
         <v>57</v>
       </c>
       <c r="B58" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C58" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F58" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.25">
@@ -2083,19 +2077,19 @@
         <v>58</v>
       </c>
       <c r="B59" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C59" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D59" t="s">
+        <v>32</v>
+      </c>
+      <c r="F59" t="s">
         <v>33</v>
       </c>
-      <c r="F59" t="s">
+      <c r="J59" t="s">
         <v>34</v>
-      </c>
-      <c r="J59" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.25">
@@ -2103,16 +2097,16 @@
         <v>59</v>
       </c>
       <c r="B60" t="s">
+        <v>106</v>
+      </c>
+      <c r="C60" t="s">
+        <v>105</v>
+      </c>
+      <c r="D60" t="s">
         <v>107</v>
       </c>
-      <c r="C60" t="s">
-        <v>106</v>
-      </c>
-      <c r="D60" t="s">
-        <v>108</v>
-      </c>
       <c r="F60" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.25">
@@ -2120,13 +2114,13 @@
         <v>60</v>
       </c>
       <c r="B61" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C61" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F61" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.25">
@@ -2134,22 +2128,22 @@
         <v>61</v>
       </c>
       <c r="B62" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C62" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D62" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F62" t="s">
+        <v>110</v>
+      </c>
+      <c r="G62" t="s">
         <v>111</v>
       </c>
-      <c r="G62" t="s">
+      <c r="H62" t="s">
         <v>112</v>
-      </c>
-      <c r="H62" t="s">
-        <v>113</v>
       </c>
       <c r="J62" t="b">
         <v>1</v>
@@ -2160,16 +2154,16 @@
         <v>62</v>
       </c>
       <c r="B63" t="s">
+        <v>133</v>
+      </c>
+      <c r="C63" t="s">
+        <v>18</v>
+      </c>
+      <c r="D63" t="s">
         <v>134</v>
       </c>
-      <c r="C63" t="s">
-        <v>19</v>
-      </c>
-      <c r="D63" t="s">
-        <v>135</v>
-      </c>
       <c r="F63" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.25">
@@ -2177,16 +2171,16 @@
         <v>63</v>
       </c>
       <c r="B64" t="s">
+        <v>135</v>
+      </c>
+      <c r="C64" t="s">
+        <v>18</v>
+      </c>
+      <c r="D64" t="s">
         <v>136</v>
       </c>
-      <c r="C64" t="s">
-        <v>19</v>
-      </c>
-      <c r="D64" t="s">
-        <v>137</v>
-      </c>
       <c r="F64" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.25">
@@ -2194,10 +2188,10 @@
         <v>64</v>
       </c>
       <c r="B65" t="s">
+        <v>137</v>
+      </c>
+      <c r="F65" t="s">
         <v>138</v>
-      </c>
-      <c r="F65" t="s">
-        <v>139</v>
       </c>
       <c r="J65">
         <v>3</v>
@@ -2221,184 +2215,184 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>142</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C2" t="s">
         <v>144</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>145</v>
-      </c>
-      <c r="D2" t="s">
-        <v>146</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C3" t="s">
+        <v>146</v>
+      </c>
+      <c r="D3" t="s">
         <v>147</v>
-      </c>
-      <c r="D3" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B4" t="s">
+        <v>148</v>
+      </c>
+      <c r="C4" t="s">
         <v>149</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>150</v>
-      </c>
-      <c r="D4" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B5" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C5" t="s">
+        <v>151</v>
+      </c>
+      <c r="D5" t="s">
         <v>152</v>
-      </c>
-      <c r="D5" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B6" t="s">
+        <v>153</v>
+      </c>
+      <c r="C6" t="s">
         <v>154</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" t="s">
         <v>155</v>
-      </c>
-      <c r="D6" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B7" t="s">
+        <v>156</v>
+      </c>
+      <c r="C7" t="s">
         <v>157</v>
       </c>
-      <c r="C7" t="s">
+      <c r="D7" t="s">
         <v>158</v>
-      </c>
-      <c r="D7" t="s">
-        <v>159</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B8" t="s">
+        <v>159</v>
+      </c>
+      <c r="C8" t="s">
         <v>160</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
         <v>161</v>
-      </c>
-      <c r="D8" t="s">
-        <v>162</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B9" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C9" t="s">
+        <v>162</v>
+      </c>
+      <c r="D9" t="s">
         <v>163</v>
-      </c>
-      <c r="D9" t="s">
-        <v>164</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B10" t="s">
+        <v>164</v>
+      </c>
+      <c r="C10" t="s">
         <v>165</v>
       </c>
-      <c r="C10" t="s">
+      <c r="D10" t="s">
         <v>166</v>
-      </c>
-      <c r="D10" t="s">
-        <v>167</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B11" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C11" t="s">
+        <v>167</v>
+      </c>
+      <c r="D11" t="s">
         <v>168</v>
-      </c>
-      <c r="D11" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B12" t="s">
+        <v>169</v>
+      </c>
+      <c r="C12" t="s">
         <v>170</v>
       </c>
-      <c r="C12" t="s">
+      <c r="D12" t="s">
         <v>171</v>
-      </c>
-      <c r="D12" t="s">
-        <v>172</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B13" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C13" t="s">
+        <v>172</v>
+      </c>
+      <c r="D13" t="s">
         <v>173</v>
-      </c>
-      <c r="D13" t="s">
-        <v>174</v>
       </c>
     </row>
   </sheetData>
@@ -2417,71 +2411,71 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>175</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>177</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>178</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>179</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>180</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>182</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>183</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>184</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>185</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>186</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>187</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B9" s="2">
         <v>64</v>
@@ -2489,7 +2483,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B10" s="2">
         <v>4</v>
@@ -2497,7 +2491,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B11" s="2">
         <v>33</v>
@@ -2505,15 +2499,15 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="B12" s="2" t="s">
         <v>191</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B13" s="3">
         <v>46146</v>
@@ -2521,7 +2515,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B14" s="3">
         <v>46146</v>
@@ -2529,31 +2523,31 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="B15" s="2" t="s">
         <v>195</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>196</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="B16" s="2" t="s">
         <v>197</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="B17" s="2" t="s">
         <v>199</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>200</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B18" s="2">
         <v>2</v>
@@ -2561,18 +2555,18 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="B19" s="2" t="s">
         <v>202</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>203</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="B20" s="2" t="s">
         <v>204</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>205</v>
       </c>
     </row>
   </sheetData>
@@ -2591,148 +2585,154 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>206</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>207</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B4" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C4" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B5" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C5" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B6" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C6" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B7" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C7" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B8" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C8" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B9" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C9" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B11" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C11" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B12" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C12" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B13" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C13" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{a4153a30-97aa-49dd-8839-66f72081522c}" enabled="1" method="Standard" siteId="{9ffff5c3-bdfa-4a9d-b595-ff68329945ef}" contentBits="0" removed="0"/>
+</clbl:labelList>
 </file>